--- a/02.FOMD/02.metadata_structure/03_FOMD_selection_criteria.xlsx
+++ b/02.FOMD/02.metadata_structure/03_FOMD_selection_criteria.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30023"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cgiar.sharepoint.com/sites/Alliance-AgroecologyKnowledgeHub/Shared Documents/General/Agroecology_Knowledge_Hub/02.FOMD/02.metadata_structure/"/>
@@ -16,7 +16,7 @@
     <sheet name="03_FOMD_selection_criteria" sheetId="1" r:id="rId1"/>
     <sheet name="03_FOMD_readme" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -66,55 +66,156 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="66">
   <si>
-    <t>criteria</t>
+    <t>screening_step</t>
+  </si>
+  <si>
+    <t>criteria_label</t>
+  </si>
+  <si>
+    <t>criteria_description</t>
   </si>
   <si>
     <t>use_for</t>
   </si>
   <si>
+    <t>level</t>
+  </si>
+  <si>
+    <t>picoc_component</t>
+  </si>
+  <si>
+    <t>outcome</t>
+  </si>
+  <si>
+    <t>full-text screening</t>
+  </si>
+  <si>
+    <t>Duplicated Record</t>
+  </si>
+  <si>
+    <t>Duplicated record</t>
+  </si>
+  <si>
     <t>exclusion</t>
   </si>
   <si>
-    <t>Dataset section</t>
-  </si>
-  <si>
-    <t>File</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Content</t>
-  </si>
-  <si>
-    <t>variable</t>
-  </si>
-  <si>
-    <t>readme</t>
-  </si>
-  <si>
-    <t>used_for</t>
-  </si>
-  <si>
-    <t>Criteria for paper selection include criteria for inclusion and for exclusion</t>
-  </si>
-  <si>
-    <t>Criterion applied in the selection of relevant meta-analyses. Among the criteria applied in the screening phase there are some criteria valid for all farming practices and some criteria farming practice specific.</t>
-  </si>
-  <si>
-    <t>screening selection criteria for systematic reviews</t>
-  </si>
-  <si>
-    <t>list of specific inclusion and exclusion criteria used to select relevant meta-analyses in the abstract and full-text screening phases.</t>
-  </si>
-  <si>
-    <t>picoc_component</t>
+    <t>first-order meta-data</t>
+  </si>
+  <si>
+    <t>general</t>
+  </si>
+  <si>
+    <t>all</t>
+  </si>
+  <si>
+    <t>Full-text Unavailable</t>
+  </si>
+  <si>
+    <t>Full-text PDF not accessible through open access, or subscriptions</t>
+  </si>
+  <si>
+    <t>Not Peer Reviewed</t>
+  </si>
+  <si>
+    <t>Record is not peer-reviewed (e.g. report, thesis, preprint)</t>
   </si>
   <si>
     <t>context</t>
   </si>
   <si>
-    <t>16_pa_selection_criteria</t>
+    <t>Other Language Text</t>
+  </si>
+  <si>
+    <t>Full text not written in English, Spanish, French or Portuguese</t>
+  </si>
+  <si>
+    <t>Not Primary Study</t>
+  </si>
+  <si>
+    <t>The record is not a primary study (e.g., meta-analysis, data paper, systematic review, vote-counting).</t>
+  </si>
+  <si>
+    <t>Retracted Record</t>
+  </si>
+  <si>
+    <t>Record was retracted</t>
+  </si>
+  <si>
+    <t>Location Not Reported</t>
+  </si>
+  <si>
+    <t>The study does not report the geographic location where the study was conducted (e.g., country, region, district, or specific site).</t>
+  </si>
+  <si>
+    <t>Study Period Not Reported</t>
+  </si>
+  <si>
+    <t>The study does not report the year or period during which the study or experiment was implemented.</t>
+  </si>
+  <si>
+    <t>Non-comparable Sampling</t>
+  </si>
+  <si>
+    <t>Outcomes for the intervention and comparator were not measured using comparable sampling methods or at comparable time points.</t>
+  </si>
+  <si>
+    <t>Non-field Experiment</t>
+  </si>
+  <si>
+    <t>The study reports experiments conducted under laboratory or greenhouse conditions rather than field conditions.</t>
+  </si>
+  <si>
+    <t>Non-agroecological Intervention</t>
+  </si>
+  <si>
+    <t>Intervention does not involve agroecological-related practices</t>
+  </si>
+  <si>
+    <t>intervention</t>
+  </si>
+  <si>
+    <t>Unclear Intervention Comparator</t>
+  </si>
+  <si>
+    <t>Intervention and comparator systems cannot be unambiguously distinguished, i.e., the management practices applied in the treatment and control cannot be distinguished (e.g., differences in crop or animal species/variety, soil management, fertiliser use, chemical inputs, shade management, planting, or harvesting practices).</t>
+  </si>
+  <si>
+    <t>intervention/comparator</t>
+  </si>
+  <si>
+    <t>Insufficient Outcome Data</t>
+  </si>
+  <si>
+    <t>Outcome means, variance estimates, and/or sample sizes required to calculate an effect size is not reported or cannot be obtained for the intervention and/or comparator</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Sole crop yields should come from the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>same experiment</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, under comparable conditions.</t>
+    </r>
+  </si>
+  <si>
+    <t>yield</t>
   </si>
   <si>
     <r>
@@ -146,175 +247,74 @@
     <t>Area basis must be consistent.</t>
   </si>
   <si>
-    <t>outcome</t>
-  </si>
-  <si>
-    <t>yield</t>
-  </si>
-  <si>
-    <t>screening_step</t>
-  </si>
-  <si>
-    <t>full-text screening</t>
-  </si>
-  <si>
-    <t>level</t>
-  </si>
-  <si>
-    <t>Full-text PDF not accessible through open access, or subscriptions</t>
+    <t>Suitable metrics for financial outcomes included monetary values (any currency) for interventions and comparators.</t>
+  </si>
+  <si>
+    <t>financial</t>
+  </si>
+  <si>
+    <t>For comparisons comparing intercropped or agroforestry systems against simplified farming systems, the land equivalent ratio was prioritized as the outcome metric while other metrics were used only when the land equivalent ratio could not be calculated.</t>
+  </si>
+  <si>
+    <t>Outcome should be at least at the level of phylum? (e.g., studies providing outcome for micro-organisims not specifying if they are bacteria, fungi, or whatever should be excluded)</t>
+  </si>
+  <si>
+    <t>biodiversity</t>
+  </si>
+  <si>
+    <t>Population is outside scope of the protocol (non-agricultural systems, non-comparison of the effect of agricultural practices)</t>
   </si>
   <si>
     <t>second and first-order meta-data</t>
   </si>
   <si>
-    <t>general</t>
-  </si>
-  <si>
-    <t>Record is not peer-reviewed (e.g. report, thesis, preprint)</t>
-  </si>
-  <si>
-    <t>first-order meta-data</t>
-  </si>
-  <si>
-    <t>Duplicated record</t>
-  </si>
-  <si>
-    <t>Record was retracted</t>
-  </si>
-  <si>
-    <t>Intervention does not involve agroecological-related practices</t>
-  </si>
-  <si>
-    <t>intervention</t>
-  </si>
-  <si>
-    <t>Population is outside scope of the protocol (non-agricultural systems, non-comparison of the effect of agricultural practices)</t>
-  </si>
-  <si>
     <t>population</t>
   </si>
   <si>
-    <t>The study does not report the geographic location where the study was conducted (e.g., country, region, district, or specific site).</t>
-  </si>
-  <si>
-    <t>The study does not report the year or period during which the study or experiment was implemented.</t>
-  </si>
-  <si>
-    <t>intervention/comparator</t>
-  </si>
-  <si>
-    <t>Intervention and comparator systems cannot be unambiguously distinguished, i.e., the management practices applied in the treatment and control cannot be distinguished (e.g., differences in crop or animal species/variety, soil management, fertiliser use, chemical inputs, shade management, planting, or harvesting practices).</t>
-  </si>
-  <si>
-    <t>Suitable metrics for financial outcomes included monetary values (any currency) for interventions and comparators.</t>
-  </si>
-  <si>
-    <t>financial</t>
-  </si>
-  <si>
-    <t>Outcome means, variance estimates, and/or sample sizes required to calculate an effect size is not reported or cannot be obtained for the intervention and/or comparator</t>
-  </si>
-  <si>
-    <t>criteria_description</t>
-  </si>
-  <si>
-    <t>The record is not a primary study (e.g., meta-analysis, data paper, systematic review, vote-counting).</t>
-  </si>
-  <si>
-    <t>Outcomes for the intervention and comparator were not measured using comparable sampling methods or at comparable time points.</t>
-  </si>
-  <si>
-    <t>The study reports experiments conducted under laboratory or greenhouse conditions rather than field conditions.</t>
-  </si>
-  <si>
-    <t>For comparisons comparing intercropped or agroforestry systems against simplified farming systems, the land equivalent ratio was prioritized as the outcome metric while other metrics were used only when the land equivalent ratio could not be calculated.</t>
-  </si>
-  <si>
-    <t>criteria_label</t>
-  </si>
-  <si>
-    <t>Duplicated Record</t>
-  </si>
-  <si>
-    <t>Full-text Unavailable</t>
-  </si>
-  <si>
-    <t>Not Peer Reviewed</t>
-  </si>
-  <si>
-    <t>Not Primary Study</t>
-  </si>
-  <si>
-    <t>Retracted Record</t>
-  </si>
-  <si>
-    <t>Location Not Reported</t>
-  </si>
-  <si>
-    <t>Study Period Not Reported</t>
-  </si>
-  <si>
-    <t>Non-comparable Sampling</t>
-  </si>
-  <si>
-    <t>Non-field Experiment</t>
-  </si>
-  <si>
-    <t>Non-agroecological Intervention</t>
-  </si>
-  <si>
-    <t>Unclear Intervention Comparator</t>
-  </si>
-  <si>
-    <t>Insufficient Outcome Data</t>
-  </si>
-  <si>
-    <t>all</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Sole crop yields should come from the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>same experiment</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>, under comparable conditions.</t>
-    </r>
-  </si>
-  <si>
-    <t>Outcome should be at least at the level of phylum? (e.g., studies providing outcome for micro-organisims not specifying if they are bacteria, fungi, or whatever should be excluded)</t>
-  </si>
-  <si>
-    <t>biodiversity</t>
-  </si>
-  <si>
-    <t>Full text not written in English, Spanish, French or Portuguese</t>
-  </si>
-  <si>
-    <t>Other Language Text</t>
+    <t>Dataset section</t>
+  </si>
+  <si>
+    <t>File</t>
+  </si>
+  <si>
+    <t>16_pa_selection_criteria</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>screening selection criteria for systematic reviews</t>
+  </si>
+  <si>
+    <t>Content</t>
+  </si>
+  <si>
+    <t>list of specific inclusion and exclusion criteria used to select relevant meta-analyses in the abstract and full-text screening phases.</t>
+  </si>
+  <si>
+    <t>variable</t>
+  </si>
+  <si>
+    <t>readme</t>
+  </si>
+  <si>
+    <t>criteria</t>
+  </si>
+  <si>
+    <t>Criterion applied in the selection of relevant meta-analyses. Among the criteria applied in the screening phase there are some criteria valid for all farming practices and some criteria farming practice specific.</t>
+  </si>
+  <si>
+    <t>used_for</t>
+  </si>
+  <si>
+    <t>Criteria for paper selection include criteria for inclusion and for exclusion</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -791,437 +791,437 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E11DDF1-D031-4606-928D-03E3D452C75A}">
   <dimension ref="A1:G29"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="21.85546875" customWidth="1"/>
     <col min="3" max="3" width="77.5703125" customWidth="1"/>
     <col min="4" max="5" width="23.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" t="s">
         <v>21</v>
       </c>
-      <c r="B1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" t="s">
         <v>23</v>
       </c>
-      <c r="F1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="C7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" t="s">
         <v>29</v>
       </c>
-      <c r="D2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" t="s">
-        <v>2</v>
-      </c>
-      <c r="E4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C5" t="s">
-        <v>64</v>
-      </c>
-      <c r="D5" t="s">
-        <v>2</v>
-      </c>
-      <c r="E5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" t="s">
-        <v>51</v>
-      </c>
-      <c r="C6" t="s">
-        <v>43</v>
-      </c>
-      <c r="D6" t="s">
-        <v>2</v>
-      </c>
-      <c r="E6" t="s">
-        <v>28</v>
-      </c>
-      <c r="F6" t="s">
-        <v>15</v>
-      </c>
-      <c r="G6" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C7" s="1" t="s">
+      <c r="C10" t="s">
         <v>30</v>
       </c>
-      <c r="D7" t="s">
-        <v>2</v>
-      </c>
-      <c r="E7" t="s">
-        <v>28</v>
-      </c>
-      <c r="F7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G7" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" t="s">
-        <v>53</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="D10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" t="s">
+        <v>18</v>
+      </c>
+      <c r="G10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" t="s">
+        <v>18</v>
+      </c>
+      <c r="G11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" t="s">
         <v>35</v>
       </c>
-      <c r="D8" t="s">
-        <v>2</v>
-      </c>
-      <c r="E8" t="s">
-        <v>28</v>
-      </c>
-      <c r="F8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G8" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="C9" s="6" t="s">
+      <c r="G12" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13" t="s">
         <v>36</v>
       </c>
-      <c r="D9" t="s">
-        <v>2</v>
-      </c>
-      <c r="E9" t="s">
-        <v>28</v>
-      </c>
-      <c r="F9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G9" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>22</v>
-      </c>
-      <c r="B10" t="s">
-        <v>55</v>
-      </c>
-      <c r="C10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D10" t="s">
-        <v>2</v>
-      </c>
-      <c r="E10" t="s">
-        <v>28</v>
-      </c>
-      <c r="F10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G10" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" t="s">
-        <v>56</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="D11" t="s">
-        <v>2</v>
-      </c>
-      <c r="E11" t="s">
-        <v>28</v>
-      </c>
-      <c r="F11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G11" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" t="s">
-        <v>57</v>
-      </c>
-      <c r="C12" t="s">
-        <v>31</v>
-      </c>
-      <c r="D12" t="s">
-        <v>2</v>
-      </c>
-      <c r="E12" t="s">
-        <v>28</v>
-      </c>
-      <c r="F12" t="s">
-        <v>32</v>
-      </c>
-      <c r="G12" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" t="s">
-        <v>58</v>
-      </c>
       <c r="C13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" t="s">
         <v>38</v>
       </c>
-      <c r="D13" t="s">
-        <v>2</v>
-      </c>
-      <c r="E13" t="s">
-        <v>28</v>
-      </c>
-      <c r="F13" t="s">
-        <v>37</v>
-      </c>
       <c r="G13" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="B14" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="C14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E14" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="G14" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7">
       <c r="D16" s="6"/>
       <c r="E16" s="6"/>
       <c r="F16" s="6"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7">
       <c r="D17" s="6"/>
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7">
       <c r="F22" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
       <c r="C23" s="6" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="F23" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G23" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
       <c r="C24" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="F24" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="G24" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
       <c r="C25" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="F25" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="G25" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
       <c r="C26" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="F26" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="G26" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
       <c r="C27" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F27" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="G27" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
       <c r="C28" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="F28" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="G28" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
       <c r="A29" s="7" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="B29" s="8"/>
       <c r="C29" s="8" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -1236,71 +1236,71 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE13B838-F287-4E84-BD57-32AF46A9650A}">
   <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="34.85546875" customWidth="1"/>
     <col min="2" max="2" width="21.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
-        <v>3</v>
+        <v>53</v>
       </c>
       <c r="B1" s="3">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2">
       <c r="A2" s="4" t="s">
-        <v>4</v>
+        <v>54</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>64</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
         <v>5</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -1309,8 +1309,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005BE3C66ACF4393458051577D36AC6C25" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="14ce307a2e56825cff9c9e7fcaaeda24">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4b26243c-b736-4d9c-b036-479be2ad88a1" xmlns:ns3="432dd258-9dce-4cb3-b611-c68c0fbce7f3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0503e52156abb22d20ee02405306de7b" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005BE3C66ACF4393458051577D36AC6C25" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1b97c7f6381d52e0ece85968e631718a">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4b26243c-b736-4d9c-b036-479be2ad88a1" xmlns:ns3="432dd258-9dce-4cb3-b611-c68c0fbce7f3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="af6cb7be8893fd4f0d362fb6f7fa19cb" ns2:_="" ns3:_="">
     <xsd:import namespace="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
     <xsd:import namespace="432dd258-9dce-4cb3-b611-c68c0fbce7f3"/>
     <xsd:element name="properties">
@@ -1504,6 +1504,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="4b26243c-b736-4d9c-b036-479be2ad88a1">
@@ -1514,49 +1523,14 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{742EC8CF-9BEB-4FCD-B5FE-5CF97BA41B98}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
-    <ds:schemaRef ds:uri="432dd258-9dce-4cb3-b611-c68c0fbce7f3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C727335A-3D73-4DE3-A820-629B896ACBED}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE21F537-F8C6-45BB-8614-D547AB26632C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
-    <ds:schemaRef ds:uri="432dd258-9dce-4cb3-b611-c68c0fbce7f3"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{31325C92-417A-44AE-8DF9-7F3FF1A39FE4}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{31325C92-417A-44AE-8DF9-7F3FF1A39FE4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE21F537-F8C6-45BB-8614-D547AB26632C}"/>
 </file>